--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -662,10 +662,10 @@
         <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
         <v>1.7</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -668,40 +668,40 @@
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -710,22 +710,22 @@
         <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46028.20833333334</v>
@@ -1025,40 +1025,40 @@
         <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="n">
         <v>2.05</v>
@@ -1067,22 +1067,22 @@
         <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46028.45833333334</v>
@@ -1501,46 +1501,46 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC9" t="n">
         <v>1.95</v>
@@ -1549,16 +1549,16 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46028.5625</v>
@@ -1620,34 +1620,34 @@
         <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
         <v>1.53</v>
@@ -1662,22 +1662,22 @@
         <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46028.58333333334</v>
@@ -1739,40 +1739,40 @@
         <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
         <v>1.91</v>
@@ -1781,22 +1781,22 @@
         <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="O11" t="n">
-        <v>4.85</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="N12" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>4.85</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="U12" t="n">
         <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -674,34 +674,34 @@
         <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
         <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -710,22 +710,22 @@
         <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46028.20833333334</v>
@@ -1028,16 +1028,16 @@
         <v>5.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
         <v>2.85</v>
@@ -1049,13 +1049,13 @@
         <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
         <v>3.25</v>
@@ -1073,16 +1073,16 @@
         <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46028.45833333334</v>
@@ -1504,10 +1504,10 @@
         <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
         <v>1.22</v>
@@ -1534,7 +1534,7 @@
         <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="AA9" t="n">
         <v>1.37</v>
@@ -1549,16 +1549,16 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46028.5625</v>
@@ -1623,13 +1623,13 @@
         <v>5.98</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
         <v>2.48</v>
@@ -1665,19 +1665,19 @@
         <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
         <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46028.58333333334</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1858,19 +1858,19 @@
         <v>1.73</v>
       </c>
       <c r="O12" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="P12" t="n">
         <v>2.16</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="T12" t="n">
         <v>2.96</v>
@@ -1879,19 +1879,19 @@
         <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
         <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
         <v>1.91</v>
@@ -1906,16 +1906,16 @@
         <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
         <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.68</v>
+        <v>5.45</v>
       </c>
       <c r="R13" t="n">
         <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="W13" t="n">
         <v>1.07</v>
@@ -2007,34 +2007,34 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.92</v>
+        <v>4.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2099,10 +2099,10 @@
         <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
@@ -2111,10 +2111,10 @@
         <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
         <v>7.1</v>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
         <v>3.4</v>
@@ -2138,22 +2138,22 @@
         <v>1.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
         <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="O2" t="n">
         <v>2.4</v>
@@ -674,10 +674,10 @@
         <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.05</v>
+        <v>4.46</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>2.75</v>
@@ -695,37 +695,37 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
         <v>3.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46028.20833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.67</v>
       </c>
       <c r="N11" t="n">
-        <v>2.47</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>4.95</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.13</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.45</v>
+        <v>2.92</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V13" t="n">
-        <v>5.85</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.07</v>
@@ -2007,34 +2007,34 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,37 +2087,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>2.13</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>5.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>7.1</v>
+        <v>5.85</v>
       </c>
       <c r="W14" t="n">
         <v>1.07</v>
@@ -2126,34 +2126,34 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>4.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.4</v>
@@ -704,10 +704,10 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
         <v>3.44</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
@@ -1073,10 +1073,10 @@
         <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
         <v>1.23</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1507,19 +1507,19 @@
         <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="T9" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
         <v>4.15</v>
@@ -1531,7 +1531,7 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z9" t="n">
         <v>5.85</v>
@@ -1549,10 +1549,10 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
@@ -1620,34 +1620,34 @@
         <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5.98</v>
+        <v>5.91</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
         <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
         <v>1.53</v>
@@ -1662,16 +1662,16 @@
         <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
         <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
         <v>1.25</v>
@@ -1739,19 +1739,19 @@
         <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>4.95</v>
+        <v>5.31</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
         <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
         <v>2.96</v>
@@ -1760,19 +1760,19 @@
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.91</v>
@@ -1781,10 +1781,10 @@
         <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
         <v>1.85</v>
@@ -1793,10 +1793,10 @@
         <v>1.87</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1867,10 +1867,10 @@
         <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
         <v>2.7</v>
@@ -1879,7 +1879,7 @@
         <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="W12" t="n">
         <v>1.08</v>
@@ -1888,10 +1888,10 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="AA12" t="n">
         <v>2.02</v>
@@ -1906,16 +1906,16 @@
         <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
         <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>2.08</v>
       </c>
       <c r="P13" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.92</v>
+        <v>5.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>5.65</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.13</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.45</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>5.85</v>
+        <v>6.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.14</v>
+        <v>3.44</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
         <v>2.3</v>
@@ -2099,7 +2099,7 @@
         <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
         <v>2.92</v>
@@ -2114,40 +2114,40 @@
         <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="W14" t="n">
         <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
         <v>1.65</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1016,37 +1016,37 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="O5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
         <v>2.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
@@ -1058,16 +1058,16 @@
         <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD5" t="n">
         <v>1.25</v>
@@ -1076,13 +1076,13 @@
         <v>1.94</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46028.45833333334</v>
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>5.91</v>
+        <v>5.96</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.28</v>
@@ -1644,22 +1644,22 @@
         <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AA10" t="n">
         <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC10" t="n">
         <v>4.25</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
         <v>5.31</v>
@@ -1754,13 +1754,13 @@
         <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
         <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
@@ -1769,25 +1769,25 @@
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD11" t="n">
         <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
         <v>1.87</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -674,16 +674,16 @@
         <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.46</v>
+        <v>4.24</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
@@ -695,13 +695,13 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -722,10 +722,10 @@
         <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46028.20833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.74</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O11" t="n">
-        <v>5.31</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>4.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.01</v>
+        <v>3.74</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>5.31</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V12" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -787,40 +787,40 @@
         <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA3" t="n">
         <v>2.3</v>
@@ -829,22 +829,22 @@
         <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46028.41319444445</v>
@@ -906,40 +906,40 @@
         <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
         <v>1.75</v>
@@ -948,22 +948,22 @@
         <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46028.41666666666</v>
@@ -1263,40 +1263,40 @@
         <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AA7" t="n">
         <v>2.23</v>
@@ -1305,22 +1305,22 @@
         <v>1.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46028.51388888889</v>
@@ -1382,40 +1382,40 @@
         <v>7.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" t="n">
         <v>1.55</v>
@@ -1430,16 +1430,16 @@
         <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46028.53125</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.74</v>
       </c>
       <c r="N11" t="n">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>5.31</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V11" t="n">
-        <v>6.95</v>
+        <v>6.8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.5</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.74</v>
+        <v>3.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>5.31</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="M5" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
@@ -1040,13 +1040,13 @@
         <v>2.83</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
@@ -1061,10 +1061,10 @@
         <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
         <v>3.9</v>
@@ -1073,10 +1073,10 @@
         <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
         <v>1.33</v>
@@ -1501,40 +1501,40 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="T9" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V9" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.85</v>
+        <v>6.01</v>
       </c>
       <c r="AA9" t="n">
         <v>1.37</v>
@@ -1549,10 +1549,10 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5.96</v>
+        <v>6.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
         <v>2.38</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="U10" t="n">
         <v>1.28</v>
@@ -1650,19 +1650,19 @@
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AA10" t="n">
         <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
         <v>1.15</v>
@@ -1671,13 +1671,13 @@
         <v>2.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46028.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.74</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O11" t="n">
-        <v>5.31</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>3.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.01</v>
+        <v>3.67</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>5.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
         <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V12" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.08</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.65</v>
+        <v>2.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>5.65</v>
+        <v>6.9</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>2.08</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>5.72</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.4</v>
+        <v>2.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>2.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -674,34 +674,34 @@
         <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.24</v>
+        <v>4.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T2" t="n">
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
         <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -710,19 +710,19 @@
         <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AH2" t="n">
         <v>2</v>
@@ -787,28 +787,28 @@
         <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U3" t="n">
         <v>1.24</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
@@ -829,13 +829,13 @@
         <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AF3" t="n">
         <v>1.72</v>
@@ -909,22 +909,22 @@
         <v>2.99</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.97</v>
+        <v>3.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
         <v>5.8</v>
@@ -933,13 +933,13 @@
         <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA4" t="n">
         <v>1.75</v>
@@ -948,16 +948,16 @@
         <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG4" t="n">
         <v>1.24</v>
@@ -1028,22 +1028,22 @@
         <v>5.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
         <v>7</v>
@@ -1052,7 +1052,7 @@
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
         <v>1.33</v>
@@ -1070,19 +1070,19 @@
         <v>3.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
         <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46028.45833333334</v>
@@ -1263,13 +1263,13 @@
         <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
         <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="R7" t="n">
         <v>1.56</v>
@@ -1299,10 +1299,10 @@
         <v>2.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AC7" t="n">
         <v>4.75</v>
@@ -1311,16 +1311,16 @@
         <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
         <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46028.51388888889</v>
@@ -1385,7 +1385,7 @@
         <v>1.91</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q8" t="n">
         <v>6.2</v>
@@ -1409,7 +1409,7 @@
         <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>1.14</v>
@@ -1439,7 +1439,7 @@
         <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46028.53125</v>
@@ -1507,34 +1507,34 @@
         <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
         <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
         <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.01</v>
+        <v>5.75</v>
       </c>
       <c r="AA9" t="n">
         <v>1.37</v>
@@ -1549,10 +1549,10 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AG9" t="n">
         <v>3</v>
@@ -1620,16 +1620,16 @@
         <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>6.02</v>
+        <v>5.97</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
         <v>2.42</v>
@@ -1641,7 +1641,7 @@
         <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -1668,16 +1668,16 @@
         <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AF10" t="n">
         <v>1.63</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46028.58333333334</v>
@@ -1745,7 +1745,7 @@
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
         <v>1.41</v>
@@ -1754,25 +1754,25 @@
         <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="AA11" t="n">
         <v>2.02</v>
@@ -1784,19 +1784,19 @@
         <v>3.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1861,25 +1861,25 @@
         <v>5.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
         <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
@@ -1888,10 +1888,10 @@
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AA12" t="n">
         <v>1.91</v>
@@ -1903,13 +1903,13 @@
         <v>3.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
         <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
         <v>1.3</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.91</v>
+        <v>5.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.08</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.72</v>
+        <v>2.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.29</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>6.85</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.51</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.39</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.67</v>
       </c>
       <c r="N11" t="n">
-        <v>2.47</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>5.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12</v>
+        <v>3.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>5.35</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>2.47</v>
       </c>
       <c r="O11" t="n">
-        <v>5.35</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.01</v>
+        <v>3.67</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>1.73</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>5.35</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.12</v>
+        <v>3.65</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>3.38</v>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.87</v>
+        <v>2.69</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.29</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2</v>
+        <v>6.85</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.7</v>
+        <v>3.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>3.38</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.69</v>
+        <v>5.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>3.29</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V14" t="n">
-        <v>6.85</v>
+        <v>5.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.36</v>
+        <v>4.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>2.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.53</v>
       </c>
       <c r="S3" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>3.42</v>
       </c>
       <c r="U3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
         <v>8.199999999999999</v>
@@ -814,31 +814,31 @@
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG3" t="n">
         <v>1.32</v>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="O4" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.08</v>
@@ -936,34 +936,34 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
         <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46028.41666666666</v>
@@ -1025,40 +1025,40 @@
         <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
         <v>2.05</v>
@@ -1067,22 +1067,22 @@
         <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
         <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46028.45833333334</v>
@@ -1144,40 +1144,40 @@
         <v>1.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA6" t="n">
         <v>1.48</v>
@@ -1192,16 +1192,16 @@
         <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46028.47916666666</v>
@@ -1263,19 +1263,19 @@
         <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
         <v>3.5</v>
@@ -1284,7 +1284,7 @@
         <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1305,22 +1305,22 @@
         <v>1.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD7" t="n">
         <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46028.51388888889</v>
@@ -1382,40 +1382,40 @@
         <v>7.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V8" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA8" t="n">
         <v>1.55</v>
@@ -1430,16 +1430,16 @@
         <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.67</v>
+        <v>3.11</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46028.53125</v>
@@ -1501,19 +1501,19 @@
         <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>6.48</v>
       </c>
       <c r="P9" t="n">
         <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
         <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
@@ -1534,7 +1534,7 @@
         <v>1.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA9" t="n">
         <v>1.37</v>
@@ -1549,16 +1549,16 @@
         <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46028.5625</v>
@@ -1620,10 +1620,10 @@
         <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>2.44</v>
@@ -1632,16 +1632,16 @@
         <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
         <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
         <v>1.01</v>
@@ -1662,22 +1662,22 @@
         <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD10" t="n">
         <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46028.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.67</v>
       </c>
       <c r="N11" t="n">
-        <v>2.47</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>5.35</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.73</v>
+        <v>2.47</v>
       </c>
       <c r="O12" t="n">
-        <v>5.35</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.65</v>
+        <v>3.24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1977,40 +1977,40 @@
         <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S13" t="n">
         <v>2.69</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
         <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>6.85</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="AA13" t="n">
         <v>1.83</v>
@@ -2022,19 +2022,19 @@
         <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2096,13 +2096,13 @@
         <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.87</v>
+        <v>6.08</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
@@ -2111,25 +2111,25 @@
         <v>3.29</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V14" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
         <v>1.8</v>
@@ -2138,22 +2138,22 @@
         <v>1.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1254,31 +1254,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.53</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U7" t="n">
         <v>1.22</v>
@@ -1287,40 +1287,40 @@
         <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
         <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46028.51388888889</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N8" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="V8" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AF8" t="n">
         <v>1.89</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46028.53125</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>6.48</v>
+        <v>5.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
         <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
         <v>4.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46028.5625</v>
@@ -1611,70 +1611,70 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.51</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
         <v>1.19</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>2.47</v>
       </c>
       <c r="O11" t="n">
-        <v>5.35</v>
+        <v>3.71</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.01</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.71</v>
+        <v>5.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V12" t="n">
-        <v>6.95</v>
+        <v>6.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>6.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>3.29</v>
       </c>
       <c r="T13" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>5.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.16</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>2.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.08</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>3.29</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="U14" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>5.45</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.53</v>
+        <v>1.39</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1356,20 +1356,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1597,17 +1597,17 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.01</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.47</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.71</v>
+        <v>5.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.04</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V11" t="n">
-        <v>6.95</v>
+        <v>6.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1845,77 +1845,77 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>2.71</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>2.23</v>
       </c>
       <c r="O12" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U12" t="n">
         <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>6.4</v>
+        <v>6.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46028.69791666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.08</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>3.29</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>5.45</v>
+        <v>7.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.2</v>
+        <v>3.16</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.53</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>6.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.85</v>
+        <v>1.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>6.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.16</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.39</v>
+        <v>2.66</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46028.70833333334</v>

--- a/jogos_2026-01-06.xlsx
+++ b/jogos_2026-01-06.xlsx
@@ -1716,17 +1716,17 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1951,90 +1951,90 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AC13" t="n">
         <v>3.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46028.70833333334</v>
@@ -2070,20 +2070,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
